--- a/projects/RNA_Aptamer_Test/Experiments/Experiment_001/Results/DPV/raw_and_baseline_data.xlsx
+++ b/projects/RNA_Aptamer_Test/Experiments/Experiment_001/Results/DPV/raw_and_baseline_data.xlsx
@@ -454,7 +454,7 @@
         <v>13.074998</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8.779163399999998</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         <v>12.691665</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3833329999999968</v>
+        <v>8.395830400000001</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>12.329165</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7458329999999975</v>
+        <v>8.033330400000001</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>12.012499</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.062498999999999</v>
+        <v>7.716664399999999</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>11.695832</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.379166</v>
+        <v>7.399997399999998</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>11.404165</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.670832999999996</v>
+        <v>7.108330400000002</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +520,7 @@
         <v>11.120831</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.954166999999998</v>
+        <v>6.8249964</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>10.858333</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.216664999999999</v>
+        <v>6.562498399999999</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         <v>10.608335</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.466662999999997</v>
+        <v>6.312500400000001</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>10.366666</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.708331999999999</v>
+        <v>6.070831399999999</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>10.133332</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.941665999999998</v>
+        <v>5.8374974</v>
       </c>
     </row>
     <row r="13">
@@ -575,7 +575,7 @@
         <v>9.920833999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>-3.154163999999998</v>
+        <v>5.6249994</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>9.724998999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>-3.349998999999999</v>
+        <v>5.429164399999999</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         <v>9.541666000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>-3.533331999999996</v>
+        <v>5.245831400000002</v>
       </c>
     </row>
     <row r="16">
@@ -608,7 +608,7 @@
         <v>9.362500000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>-3.712497999999997</v>
+        <v>5.066665400000002</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +619,7 @@
         <v>9.183333000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>-3.891664999999996</v>
+        <v>4.887498400000002</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         <v>9.029166699999999</v>
       </c>
       <c r="C18" t="n">
-        <v>-4.045831299999998</v>
+        <v>4.7333321</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>8.887501</v>
       </c>
       <c r="C19" t="n">
-        <v>-4.187496999999997</v>
+        <v>4.591666400000001</v>
       </c>
     </row>
     <row r="20">
@@ -652,7 +652,7 @@
         <v>8.770834600000001</v>
       </c>
       <c r="C20" t="n">
-        <v>-4.304163399999997</v>
+        <v>4.475000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -663,7 +663,7 @@
         <v>8.641665799999998</v>
       </c>
       <c r="C21" t="n">
-        <v>-4.433332199999999</v>
+        <v>4.345831199999999</v>
       </c>
     </row>
     <row r="22">
@@ -674,7 +674,7 @@
         <v>8.516666600000001</v>
       </c>
       <c r="C22" t="n">
-        <v>-4.558331399999997</v>
+        <v>4.220832000000001</v>
       </c>
     </row>
     <row r="23">
@@ -685,7 +685,7 @@
         <v>8.366667199999998</v>
       </c>
       <c r="C23" t="n">
-        <v>-4.708330799999999</v>
+        <v>4.070832599999999</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +696,7 @@
         <v>8.220833499999999</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.854164499999998</v>
+        <v>3.9249989</v>
       </c>
     </row>
     <row r="25">
@@ -707,7 +707,7 @@
         <v>8.079167</v>
       </c>
       <c r="C25" t="n">
-        <v>-4.995830999999997</v>
+        <v>3.783332400000001</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         <v>7.950000040000001</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.124997959999996</v>
+        <v>3.654165440000002</v>
       </c>
     </row>
     <row r="27">
@@ -729,7 +729,7 @@
         <v>7.8208337</v>
       </c>
       <c r="C27" t="n">
-        <v>-5.254164299999998</v>
+        <v>3.5249991</v>
       </c>
     </row>
     <row r="28">
@@ -740,7 +740,7 @@
         <v>7.666666375</v>
       </c>
       <c r="C28" t="n">
-        <v>-5.408331624999997</v>
+        <v>3.370831775000001</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +751,7 @@
         <v>7.495833360000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-5.579164639999997</v>
+        <v>3.199998760000001</v>
       </c>
     </row>
     <row r="30">
@@ -762,7 +762,7 @@
         <v>7.3208335</v>
       </c>
       <c r="C30" t="n">
-        <v>-5.754164499999997</v>
+        <v>3.024998900000001</v>
       </c>
     </row>
     <row r="31">
@@ -773,7 +773,7 @@
         <v>7.1416668</v>
       </c>
       <c r="C31" t="n">
-        <v>-5.933331199999997</v>
+        <v>2.845832200000001</v>
       </c>
     </row>
     <row r="32">
@@ -784,7 +784,7 @@
         <v>6.9624996</v>
       </c>
       <c r="C32" t="n">
-        <v>-6.112498399999997</v>
+        <v>2.666665000000001</v>
       </c>
     </row>
     <row r="33">
@@ -795,7 +795,7 @@
         <v>6.7583334</v>
       </c>
       <c r="C33" t="n">
-        <v>-6.316664599999998</v>
+        <v>2.462498800000001</v>
       </c>
     </row>
     <row r="34">
@@ -806,7 +806,7 @@
         <v>6.5708336</v>
       </c>
       <c r="C34" t="n">
-        <v>-6.504164399999997</v>
+        <v>2.274999000000001</v>
       </c>
     </row>
     <row r="35">
@@ -817,7 +817,7 @@
         <v>6.375</v>
       </c>
       <c r="C35" t="n">
-        <v>-6.699997999999997</v>
+        <v>2.079165400000001</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>6.2041667</v>
       </c>
       <c r="C36" t="n">
-        <v>-6.870831299999997</v>
+        <v>1.908332100000001</v>
       </c>
     </row>
     <row r="37">
@@ -839,7 +839,7 @@
         <v>6.0041665</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.070831499999997</v>
+        <v>1.708331900000001</v>
       </c>
     </row>
     <row r="38">
@@ -850,7 +850,7 @@
         <v>5.8208333</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.254164699999997</v>
+        <v>1.524998700000001</v>
       </c>
     </row>
     <row r="39">
@@ -861,7 +861,7 @@
         <v>5.6333332</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.441664799999997</v>
+        <v>1.337498600000001</v>
       </c>
     </row>
     <row r="40">
@@ -872,7 +872,7 @@
         <v>5.4666667</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.608331299999997</v>
+        <v>1.170832100000001</v>
       </c>
     </row>
     <row r="41">
@@ -883,7 +883,7 @@
         <v>5.29999995</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.774998049999997</v>
+        <v>1.004165350000001</v>
       </c>
     </row>
     <row r="42">
@@ -894,7 +894,7 @@
         <v>5.150000334</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.924997665999998</v>
+        <v>0.8541657340000004</v>
       </c>
     </row>
     <row r="43">
@@ -905,7 +905,7 @@
         <v>5.008333299999999</v>
       </c>
       <c r="C43" t="n">
-        <v>-8.066664699999997</v>
+        <v>0.7124987000000003</v>
       </c>
     </row>
     <row r="44">
@@ -916,7 +916,7 @@
         <v>4.8791669</v>
       </c>
       <c r="C44" t="n">
-        <v>-8.195831099999998</v>
+        <v>0.5833323000000004</v>
       </c>
     </row>
     <row r="45">
@@ -927,7 +927,7 @@
         <v>4.745833699999999</v>
       </c>
       <c r="C45" t="n">
-        <v>-8.329164299999999</v>
+        <v>0.4499991000000003</v>
       </c>
     </row>
     <row r="46">
@@ -938,7 +938,7 @@
         <v>4.6374996</v>
       </c>
       <c r="C46" t="n">
-        <v>-8.437498399999997</v>
+        <v>0.3416650000000008</v>
       </c>
     </row>
     <row r="47">
@@ -949,7 +949,7 @@
         <v>4.5625</v>
       </c>
       <c r="C47" t="n">
-        <v>-8.512497999999997</v>
+        <v>0.2666654000000008</v>
       </c>
     </row>
     <row r="48">
@@ -960,7 +960,7 @@
         <v>4.4999997</v>
       </c>
       <c r="C48" t="n">
-        <v>-8.574998299999997</v>
+        <v>0.2041651000000009</v>
       </c>
     </row>
     <row r="49">
@@ -971,7 +971,7 @@
         <v>4.4416666</v>
       </c>
       <c r="C49" t="n">
-        <v>-8.633331399999998</v>
+        <v>0.1458320000000004</v>
       </c>
     </row>
     <row r="50">
@@ -982,7 +982,7 @@
         <v>4.3875003</v>
       </c>
       <c r="C50" t="n">
-        <v>-8.687497699999998</v>
+        <v>0.09166570000000096</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +993,7 @@
         <v>4.3458333</v>
       </c>
       <c r="C51" t="n">
-        <v>-8.729164699999998</v>
+        <v>0.04999870000000062</v>
       </c>
     </row>
     <row r="52">
@@ -1004,7 +1004,7 @@
         <v>4.3125</v>
       </c>
       <c r="C52" t="n">
-        <v>-8.762497999999997</v>
+        <v>0.01666540000000083</v>
       </c>
     </row>
     <row r="53">
@@ -1015,7 +1015,7 @@
         <v>4.291666999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>-8.783330999999997</v>
+        <v>-0.004167599999999716</v>
       </c>
     </row>
     <row r="54">
@@ -1026,7 +1026,7 @@
         <v>4.295834599999999</v>
       </c>
       <c r="C54" t="n">
-        <v>-8.779163399999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1037,7 +1037,7 @@
         <v>4.3125</v>
       </c>
       <c r="C55" t="n">
-        <v>-8.762497999999997</v>
+        <v>0.01666540000000083</v>
       </c>
     </row>
     <row r="56">
@@ -1048,7 +1048,7 @@
         <v>4.324999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>-8.749997999999998</v>
+        <v>0.02916540000000012</v>
       </c>
     </row>
     <row r="57">
@@ -1059,7 +1059,7 @@
         <v>4.345833000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-8.729164999999997</v>
+        <v>0.04999840000000155</v>
       </c>
     </row>
     <row r="58">
@@ -1070,7 +1070,7 @@
         <v>4.379166</v>
       </c>
       <c r="C58" t="n">
-        <v>-8.695831999999998</v>
+        <v>0.0833314000000005</v>
       </c>
     </row>
     <row r="59">
@@ -1081,7 +1081,7 @@
         <v>4.416667</v>
       </c>
       <c r="C59" t="n">
-        <v>-8.658330999999997</v>
+        <v>0.1208324000000012</v>
       </c>
     </row>
     <row r="60">
@@ -1092,7 +1092,7 @@
         <v>4.454167</v>
       </c>
       <c r="C60" t="n">
-        <v>-8.620830999999997</v>
+        <v>0.1583324000000008</v>
       </c>
     </row>
     <row r="61">
@@ -1103,7 +1103,7 @@
         <v>4.4791665</v>
       </c>
       <c r="C61" t="n">
-        <v>-8.595831499999997</v>
+        <v>0.1833319000000007</v>
       </c>
     </row>
     <row r="62">
@@ -1114,7 +1114,7 @@
         <v>4.520834</v>
       </c>
       <c r="C62" t="n">
-        <v>-8.554163999999997</v>
+        <v>0.2249994000000006</v>
       </c>
     </row>
     <row r="63">
@@ -1125,7 +1125,7 @@
         <v>4.566667499999999</v>
       </c>
       <c r="C63" t="n">
-        <v>-8.508330499999998</v>
+        <v>0.2708329000000003</v>
       </c>
     </row>
     <row r="64">
@@ -1136,7 +1136,7 @@
         <v>4.629166000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>-8.445831999999996</v>
+        <v>0.3333314000000014</v>
       </c>
     </row>
     <row r="65">
@@ -1147,7 +1147,7 @@
         <v>4.695834</v>
       </c>
       <c r="C65" t="n">
-        <v>-8.379163999999998</v>
+        <v>0.3999994000000004</v>
       </c>
     </row>
     <row r="66">
@@ -1158,7 +1158,7 @@
         <v>4.7583337</v>
       </c>
       <c r="C66" t="n">
-        <v>-8.316664299999998</v>
+        <v>0.4624991000000005</v>
       </c>
     </row>
     <row r="67">
@@ -1169,7 +1169,7 @@
         <v>4.8333326</v>
       </c>
       <c r="C67" t="n">
-        <v>-8.241665399999997</v>
+        <v>0.5374980000000011</v>
       </c>
     </row>
     <row r="68">
@@ -1180,7 +1180,7 @@
         <v>4.891666499999999</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.183331499999998</v>
+        <v>0.5958319000000003</v>
       </c>
     </row>
     <row r="69">
@@ -1191,7 +1191,7 @@
         <v>4.970834</v>
       </c>
       <c r="C69" t="n">
-        <v>-8.104163999999997</v>
+        <v>0.6749994000000008</v>
       </c>
     </row>
     <row r="70">
@@ -1202,7 +1202,7 @@
         <v>5.0375</v>
       </c>
       <c r="C70" t="n">
-        <v>-8.037497999999998</v>
+        <v>0.7416654000000005</v>
       </c>
     </row>
     <row r="71">
@@ -1213,7 +1213,7 @@
         <v>5.108333</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.966664999999997</v>
+        <v>0.8124984000000008</v>
       </c>
     </row>
     <row r="72">
@@ -1224,7 +1224,7 @@
         <v>5.179167999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.895829999999998</v>
+        <v>0.8833333999999997</v>
       </c>
     </row>
     <row r="73">
@@ -1235,7 +1235,7 @@
         <v>5.245832</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.829165999999997</v>
+        <v>0.9499974000000009</v>
       </c>
     </row>
     <row r="74">
@@ -1246,7 +1246,7 @@
         <v>5.325001</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.749996999999997</v>
+        <v>1.029166400000001</v>
       </c>
     </row>
     <row r="75">
@@ -1257,7 +1257,7 @@
         <v>5.383334999999999</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.691662999999998</v>
+        <v>1.0875004</v>
       </c>
     </row>
     <row r="76">
@@ -1268,7 +1268,7 @@
         <v>5.445834</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.629163999999998</v>
+        <v>1.1499994</v>
       </c>
     </row>
     <row r="77">
@@ -1279,7 +1279,7 @@
         <v>5.512501</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.562496999999997</v>
+        <v>1.216666400000001</v>
       </c>
     </row>
     <row r="78">
@@ -1290,7 +1290,7 @@
         <v>5.591667000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.483330999999996</v>
+        <v>1.295832400000002</v>
       </c>
     </row>
     <row r="79">
@@ -1301,7 +1301,7 @@
         <v>5.654168000000002</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.420829999999995</v>
+        <v>1.358333400000003</v>
       </c>
     </row>
     <row r="80">
@@ -1312,7 +1312,7 @@
         <v>5.708334999999998</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.366662999999999</v>
+        <v>1.412500399999999</v>
       </c>
     </row>
     <row r="81">
@@ -1323,7 +1323,7 @@
         <v>5.754167999999998</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.320829999999999</v>
+        <v>1.458333399999999</v>
       </c>
     </row>
     <row r="82">
@@ -1334,7 +1334,7 @@
         <v>5.791666999999999</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.283330999999999</v>
+        <v>1.495832399999999</v>
       </c>
     </row>
     <row r="83">
@@ -1345,7 +1345,7 @@
         <v>5.841665999999998</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.233331999999999</v>
+        <v>1.545831399999999</v>
       </c>
     </row>
     <row r="84">
@@ -1356,7 +1356,7 @@
         <v>5.895830999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.179166999999998</v>
+        <v>1.5999964</v>
       </c>
     </row>
     <row r="85">
@@ -1367,7 +1367,7 @@
         <v>5.966666</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.108331999999997</v>
+        <v>1.670831400000001</v>
       </c>
     </row>
     <row r="86">
@@ -1378,7 +1378,7 @@
         <v>6.020835000000002</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.054162999999996</v>
+        <v>1.725000400000003</v>
       </c>
     </row>
     <row r="87">
@@ -1389,7 +1389,7 @@
         <v>6.062501000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.012496999999996</v>
+        <v>1.766666400000002</v>
       </c>
     </row>
     <row r="88">
@@ -1400,7 +1400,7 @@
         <v>6.100000000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>-6.974997999999996</v>
+        <v>1.804165400000002</v>
       </c>
     </row>
     <row r="89">
@@ -1411,7 +1411,7 @@
         <v>6.129167000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>-6.945830999999997</v>
+        <v>1.833332400000002</v>
       </c>
     </row>
     <row r="90">
@@ -1422,7 +1422,7 @@
         <v>6.158334</v>
       </c>
       <c r="C90" t="n">
-        <v>-6.916663999999997</v>
+        <v>1.862499400000001</v>
       </c>
     </row>
     <row r="91">
@@ -1433,7 +1433,7 @@
         <v>6.199999999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>-6.874997999999998</v>
+        <v>1.9041654</v>
       </c>
     </row>
     <row r="92">
@@ -1444,7 +1444,7 @@
         <v>6.245834</v>
       </c>
       <c r="C92" t="n">
-        <v>-6.829163999999997</v>
+        <v>1.949999400000001</v>
       </c>
     </row>
     <row r="93">
@@ -1455,7 +1455,7 @@
         <v>6.287499000000002</v>
       </c>
       <c r="C93" t="n">
-        <v>-6.787498999999995</v>
+        <v>1.991664400000003</v>
       </c>
     </row>
     <row r="94">
@@ -1466,7 +1466,7 @@
         <v>6.320834</v>
       </c>
       <c r="C94" t="n">
-        <v>-6.754163999999998</v>
+        <v>2.0249994</v>
       </c>
     </row>
     <row r="95">
@@ -1477,7 +1477,7 @@
         <v>6.333333</v>
       </c>
       <c r="C95" t="n">
-        <v>-6.741664999999998</v>
+        <v>2.0374984</v>
       </c>
     </row>
     <row r="96">
@@ -1488,7 +1488,7 @@
         <v>6.350001000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>-6.724996999999997</v>
+        <v>2.054166400000002</v>
       </c>
     </row>
     <row r="97">
@@ -1499,7 +1499,7 @@
         <v>6.362501999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>-6.712495999999998</v>
+        <v>2.0666674</v>
       </c>
     </row>
     <row r="98">
@@ -1510,7 +1510,7 @@
         <v>6.391666999999998</v>
       </c>
       <c r="C98" t="n">
-        <v>-6.683330999999999</v>
+        <v>2.095832399999999</v>
       </c>
     </row>
     <row r="99">
@@ -1521,7 +1521,7 @@
         <v>6.412498999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>-6.662498999999999</v>
+        <v>2.116664399999999</v>
       </c>
     </row>
     <row r="100">
@@ -1532,7 +1532,7 @@
         <v>6.420831</v>
       </c>
       <c r="C100" t="n">
-        <v>-6.654166999999998</v>
+        <v>2.124996400000001</v>
       </c>
     </row>
     <row r="101">
@@ -1543,7 +1543,7 @@
         <v>6.412500999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>-6.662496999999998</v>
+        <v>2.1166664</v>
       </c>
     </row>
     <row r="102">
@@ -1554,7 +1554,7 @@
         <v>6.400002000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>-6.674995999999997</v>
+        <v>2.104167400000001</v>
       </c>
     </row>
     <row r="103">
@@ -1565,7 +1565,7 @@
         <v>6.370834000000002</v>
       </c>
       <c r="C103" t="n">
-        <v>-6.704163999999995</v>
+        <v>2.074999400000003</v>
       </c>
     </row>
     <row r="104">
@@ -1576,7 +1576,7 @@
         <v>6.362501000000002</v>
       </c>
       <c r="C104" t="n">
-        <v>-6.712496999999995</v>
+        <v>2.066666400000003</v>
       </c>
     </row>
     <row r="105">
@@ -1587,7 +1587,7 @@
         <v>6.349999</v>
       </c>
       <c r="C105" t="n">
-        <v>-6.724998999999997</v>
+        <v>2.054164400000001</v>
       </c>
     </row>
     <row r="106">
@@ -1598,7 +1598,7 @@
         <v>6.349999</v>
       </c>
       <c r="C106" t="n">
-        <v>-6.724998999999997</v>
+        <v>2.054164400000001</v>
       </c>
     </row>
     <row r="107">
@@ -1609,7 +1609,7 @@
         <v>6.324998999999998</v>
       </c>
       <c r="C107" t="n">
-        <v>-6.749998999999999</v>
+        <v>2.029164399999999</v>
       </c>
     </row>
     <row r="108">
@@ -1620,7 +1620,7 @@
         <v>6.3125</v>
       </c>
       <c r="C108" t="n">
-        <v>-6.762497999999997</v>
+        <v>2.016665400000001</v>
       </c>
     </row>
     <row r="109">
@@ -1631,7 +1631,7 @@
         <v>6.295834000000003</v>
       </c>
       <c r="C109" t="n">
-        <v>-6.779163999999994</v>
+        <v>1.999999400000004</v>
       </c>
     </row>
     <row r="110">
@@ -1642,7 +1642,7 @@
         <v>6.266669</v>
       </c>
       <c r="C110" t="n">
-        <v>-6.808328999999997</v>
+        <v>1.970834400000001</v>
       </c>
     </row>
     <row r="111">
@@ -1653,7 +1653,7 @@
         <v>6.224999</v>
       </c>
       <c r="C111" t="n">
-        <v>-6.849998999999997</v>
+        <v>1.929164400000001</v>
       </c>
     </row>
     <row r="112">
@@ -1664,7 +1664,7 @@
         <v>6.1875</v>
       </c>
       <c r="C112" t="n">
-        <v>-6.887497999999997</v>
+        <v>1.891665400000001</v>
       </c>
     </row>
     <row r="113">
@@ -1675,7 +1675,7 @@
         <v>6.145834000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>-6.929163999999997</v>
+        <v>1.849999400000002</v>
       </c>
     </row>
     <row r="114">
@@ -1686,7 +1686,7 @@
         <v>6.108333999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>-6.966663999999998</v>
+        <v>1.8124994</v>
       </c>
     </row>
     <row r="115">
@@ -1697,7 +1697,7 @@
         <v>6.066666000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.008331999999996</v>
+        <v>1.770831400000002</v>
       </c>
     </row>
     <row r="116">
@@ -1708,7 +1708,7 @@
         <v>6.020831000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.054166999999996</v>
+        <v>1.724996400000002</v>
       </c>
     </row>
     <row r="117">
@@ -1719,7 +1719,7 @@
         <v>5.966664999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.108332999999998</v>
+        <v>1.6708304</v>
       </c>
     </row>
     <row r="118">
@@ -1730,7 +1730,7 @@
         <v>5.933330999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.141666999999998</v>
+        <v>1.6374964</v>
       </c>
     </row>
     <row r="119">
@@ -1741,7 +1741,7 @@
         <v>5.899999999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.174997999999999</v>
+        <v>1.604165399999999</v>
       </c>
     </row>
     <row r="120">
@@ -1752,7 +1752,7 @@
         <v>5.833331999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.241665999999999</v>
+        <v>1.537497399999999</v>
       </c>
     </row>
     <row r="121">
@@ -1763,7 +1763,7 @@
         <v>5.737497999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.337499999999999</v>
+        <v>1.441663399999999</v>
       </c>
     </row>
     <row r="122">
@@ -1774,7 +1774,7 @@
         <v>5.662499</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.412498999999997</v>
+        <v>1.366664400000001</v>
       </c>
     </row>
     <row r="123">
@@ -1785,7 +1785,7 @@
         <v>5.616665000000001</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.458332999999996</v>
+        <v>1.320830400000002</v>
       </c>
     </row>
     <row r="124">
@@ -1796,7 +1796,7 @@
         <v>5.545833999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.529163999999998</v>
+        <v>1.2499994</v>
       </c>
     </row>
     <row r="125">
@@ -1807,7 +1807,7 @@
         <v>5.479164999999998</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.595832999999999</v>
+        <v>1.183330399999999</v>
       </c>
     </row>
     <row r="126">
@@ -1818,7 +1818,7 @@
         <v>5.408328999999998</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.666668999999999</v>
+        <v>1.112494399999999</v>
       </c>
     </row>
     <row r="127">
@@ -1829,7 +1829,7 @@
         <v>5.358333000000002</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.716664999999995</v>
+        <v>1.062498400000003</v>
       </c>
     </row>
     <row r="128">
@@ -1840,7 +1840,7 @@
         <v>5.274998</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.799999999999997</v>
+        <v>0.9791634000000009</v>
       </c>
     </row>
     <row r="129">
@@ -1851,7 +1851,7 @@
         <v>5.208334000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.866663999999997</v>
+        <v>0.9124994000000015</v>
       </c>
     </row>
     <row r="130">
@@ -1862,7 +1862,7 @@
         <v>5.145834000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.929163999999997</v>
+        <v>0.8499994000000015</v>
       </c>
     </row>
     <row r="131">
@@ -1873,7 +1873,7 @@
         <v>5.091666999999998</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.983331</v>
+        <v>0.7958323999999983</v>
       </c>
     </row>
     <row r="132">
@@ -1884,7 +1884,7 @@
         <v>5.016667999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>-8.058329999999998</v>
+        <v>0.7208334000000001</v>
       </c>
     </row>
     <row r="133">
@@ -1895,7 +1895,7 @@
         <v>4.941667000000002</v>
       </c>
       <c r="C133" t="n">
-        <v>-8.133330999999995</v>
+        <v>0.6458324000000033</v>
       </c>
     </row>
     <row r="134">
@@ -1906,7 +1906,7 @@
         <v>4.883333</v>
       </c>
       <c r="C134" t="n">
-        <v>-8.191664999999997</v>
+        <v>0.5874984000000012</v>
       </c>
     </row>
     <row r="135">
@@ -1917,7 +1917,7 @@
         <v>4.8125</v>
       </c>
       <c r="C135" t="n">
-        <v>-8.262497999999997</v>
+        <v>0.5166654000000008</v>
       </c>
     </row>
     <row r="136">
@@ -1928,7 +1928,7 @@
         <v>4.741664999999998</v>
       </c>
       <c r="C136" t="n">
-        <v>-8.333333</v>
+        <v>0.4458303999999984</v>
       </c>
     </row>
     <row r="137">
@@ -1939,7 +1939,7 @@
         <v>4.670831999999997</v>
       </c>
       <c r="C137" t="n">
-        <v>-8.404166</v>
+        <v>0.374997399999998</v>
       </c>
     </row>
     <row r="138">
@@ -1950,7 +1950,7 @@
         <v>4.599998999999997</v>
       </c>
       <c r="C138" t="n">
-        <v>-8.474999</v>
+        <v>0.3041643999999977</v>
       </c>
     </row>
     <row r="139">
@@ -1961,7 +1961,7 @@
         <v>4.537502999999997</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.537495</v>
+        <v>0.2416683999999982</v>
       </c>
     </row>
     <row r="140">
@@ -1972,7 +1972,7 @@
         <v>4.470832999999999</v>
       </c>
       <c r="C140" t="n">
-        <v>-8.604164999999998</v>
+        <v>0.1749983999999998</v>
       </c>
     </row>
     <row r="141">
@@ -1983,7 +1983,7 @@
         <v>4.420833999999999</v>
       </c>
       <c r="C141" t="n">
-        <v>-8.654163999999998</v>
+        <v>0.1249994000000001</v>
       </c>
     </row>
     <row r="142">
@@ -1994,7 +1994,7 @@
         <v>4.354165999999999</v>
       </c>
       <c r="C142" t="n">
-        <v>-8.720831999999998</v>
+        <v>0.05833140000000014</v>
       </c>
     </row>
     <row r="143">
@@ -2005,7 +2005,7 @@
         <v>4.295836000000001</v>
       </c>
       <c r="C143" t="n">
-        <v>-8.779161999999996</v>
+        <v>1.400000002149682e-06</v>
       </c>
     </row>
     <row r="144">
@@ -2016,7 +2016,7 @@
         <v>4.229168999999999</v>
       </c>
       <c r="C144" t="n">
-        <v>-8.845828999999998</v>
+        <v>-0.06666560000000032</v>
       </c>
     </row>
     <row r="145">
@@ -2027,7 +2027,7 @@
         <v>4.183333999999999</v>
       </c>
       <c r="C145" t="n">
-        <v>-8.891663999999999</v>
+        <v>-0.1125006000000006</v>
       </c>
     </row>
     <row r="146">
@@ -2038,7 +2038,7 @@
         <v>4.112500000000001</v>
       </c>
       <c r="C146" t="n">
-        <v>-8.962497999999997</v>
+        <v>-0.1833345999999985</v>
       </c>
     </row>
     <row r="147">
@@ -2049,7 +2049,7 @@
         <v>4.058334000000002</v>
       </c>
       <c r="C147" t="n">
-        <v>-9.016663999999995</v>
+        <v>-0.2375005999999971</v>
       </c>
     </row>
     <row r="148">
@@ -2060,7 +2060,7 @@
         <v>3.995832999999998</v>
       </c>
       <c r="C148" t="n">
-        <v>-9.079165</v>
+        <v>-0.3000016000000016</v>
       </c>
     </row>
     <row r="149">
@@ -2071,7 +2071,7 @@
         <v>3.958331999999999</v>
       </c>
       <c r="C149" t="n">
-        <v>-9.116665999999999</v>
+        <v>-0.3375026000000005</v>
       </c>
     </row>
     <row r="150">
@@ -2082,7 +2082,7 @@
         <v>3.895831999999999</v>
       </c>
       <c r="C150" t="n">
-        <v>-9.179165999999999</v>
+        <v>-0.4000026000000005</v>
       </c>
     </row>
     <row r="151">
@@ -2093,7 +2093,7 @@
         <v>3.849997999999999</v>
       </c>
       <c r="C151" t="n">
-        <v>-9.224999999999998</v>
+        <v>-0.4458365999999998</v>
       </c>
     </row>
     <row r="152">
@@ -2104,7 +2104,7 @@
         <v>3.770831999999999</v>
       </c>
       <c r="C152" t="n">
-        <v>-9.304165999999999</v>
+        <v>-0.5250026000000005</v>
       </c>
     </row>
     <row r="153">
@@ -2115,7 +2115,7 @@
         <v>3.725000000000001</v>
       </c>
       <c r="C153" t="n">
-        <v>-9.349997999999996</v>
+        <v>-0.5708345999999977</v>
       </c>
     </row>
     <row r="154">
@@ -2126,7 +2126,7 @@
         <v>3.670832000000001</v>
       </c>
       <c r="C154" t="n">
-        <v>-9.404165999999996</v>
+        <v>-0.6250025999999984</v>
       </c>
     </row>
     <row r="155">
@@ -2137,7 +2137,7 @@
         <v>3.654167000000001</v>
       </c>
       <c r="C155" t="n">
-        <v>-9.420830999999996</v>
+        <v>-0.6416675999999981</v>
       </c>
     </row>
     <row r="156">
@@ -2148,7 +2148,7 @@
         <v>3.637500000000001</v>
       </c>
       <c r="C156" t="n">
-        <v>-9.437497999999996</v>
+        <v>-0.6583345999999981</v>
       </c>
     </row>
     <row r="157">
@@ -2159,7 +2159,7 @@
         <v>3.616666999999998</v>
       </c>
       <c r="C157" t="n">
-        <v>-9.458330999999999</v>
+        <v>-0.6791676000000013</v>
       </c>
     </row>
     <row r="158">
@@ -2170,7 +2170,7 @@
         <v>3.595833000000001</v>
       </c>
       <c r="C158" t="n">
-        <v>-9.479164999999997</v>
+        <v>-0.7000015999999984</v>
       </c>
     </row>
     <row r="159">
@@ -2181,7 +2181,7 @@
         <v>3.550001</v>
       </c>
       <c r="C159" t="n">
-        <v>-9.524996999999997</v>
+        <v>-0.7458335999999992</v>
       </c>
     </row>
     <row r="160">
@@ -2192,7 +2192,7 @@
         <v>3.512502999999999</v>
       </c>
       <c r="C160" t="n">
-        <v>-9.562494999999998</v>
+        <v>-0.7833316000000003</v>
       </c>
     </row>
     <row r="161">
@@ -2203,7 +2203,7 @@
         <v>3.454167000000002</v>
       </c>
       <c r="C161" t="n">
-        <v>-9.620830999999995</v>
+        <v>-0.8416675999999974</v>
       </c>
     </row>
     <row r="162">
@@ -2214,7 +2214,7 @@
         <v>3.425000999999998</v>
       </c>
       <c r="C162" t="n">
-        <v>-9.649996999999999</v>
+        <v>-0.870833600000001</v>
       </c>
     </row>
     <row r="163">
@@ -2225,7 +2225,7 @@
         <v>3.395834000000001</v>
       </c>
       <c r="C163" t="n">
-        <v>-9.679163999999997</v>
+        <v>-0.9000005999999985</v>
       </c>
     </row>
     <row r="164">
@@ -2236,7 +2236,7 @@
         <v>3.383334</v>
       </c>
       <c r="C164" t="n">
-        <v>-9.691663999999998</v>
+        <v>-0.9125005999999996</v>
       </c>
     </row>
     <row r="165">
@@ -2247,7 +2247,7 @@
         <v>3.358332000000001</v>
       </c>
       <c r="C165" t="n">
-        <v>-9.716665999999996</v>
+        <v>-0.9375025999999984</v>
       </c>
     </row>
     <row r="166">
@@ -2258,7 +2258,7 @@
         <v>3.316668000000002</v>
       </c>
       <c r="C166" t="n">
-        <v>-9.758329999999996</v>
+        <v>-0.9791665999999974</v>
       </c>
     </row>
     <row r="167">
@@ -2269,7 +2269,7 @@
         <v>3.283334</v>
       </c>
       <c r="C167" t="n">
-        <v>-9.791663999999997</v>
+        <v>-1.012500599999999</v>
       </c>
     </row>
     <row r="168">
@@ -2280,7 +2280,7 @@
         <v>3.270834999999998</v>
       </c>
       <c r="C168" t="n">
-        <v>-9.804162999999999</v>
+        <v>-1.024999600000001</v>
       </c>
     </row>
     <row r="169">
@@ -2291,7 +2291,7 @@
         <v>3.270832999999998</v>
       </c>
       <c r="C169" t="n">
-        <v>-9.804164999999999</v>
+        <v>-1.025001600000001</v>
       </c>
     </row>
     <row r="170">
@@ -2302,7 +2302,7 @@
         <v>3.270833</v>
       </c>
       <c r="C170" t="n">
-        <v>-9.804164999999998</v>
+        <v>-1.0250016</v>
       </c>
     </row>
     <row r="171">
@@ -2313,7 +2313,7 @@
         <v>3.287499</v>
       </c>
       <c r="C171" t="n">
-        <v>-9.787498999999997</v>
+        <v>-1.008335599999999</v>
       </c>
     </row>
     <row r="172">
@@ -2324,7 +2324,7 @@
         <v>3.291667</v>
       </c>
       <c r="C172" t="n">
-        <v>-9.783330999999997</v>
+        <v>-1.004167599999999</v>
       </c>
     </row>
     <row r="173">
@@ -2335,7 +2335,7 @@
         <v>3.2875</v>
       </c>
       <c r="C173" t="n">
-        <v>-9.787497999999998</v>
+        <v>-1.0083346</v>
       </c>
     </row>
     <row r="174">
@@ -2346,7 +2346,7 @@
         <v>3.254167000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>-9.820830999999997</v>
+        <v>-1.041667599999998</v>
       </c>
     </row>
     <row r="175">
@@ -2357,7 +2357,7 @@
         <v>3.258334</v>
       </c>
       <c r="C175" t="n">
-        <v>-9.816663999999998</v>
+        <v>-1.0375006</v>
       </c>
     </row>
     <row r="176">
@@ -2368,7 +2368,7 @@
         <v>3.274999999999999</v>
       </c>
       <c r="C176" t="n">
-        <v>-9.799997999999999</v>
+        <v>-1.020834600000001</v>
       </c>
     </row>
     <row r="177">
@@ -2379,7 +2379,7 @@
         <v>3.275001</v>
       </c>
       <c r="C177" t="n">
-        <v>-9.799996999999998</v>
+        <v>-1.0208336</v>
       </c>
     </row>
     <row r="178">
@@ -2390,7 +2390,7 @@
         <v>3.245833000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>-9.829164999999996</v>
+        <v>-1.050001599999998</v>
       </c>
     </row>
     <row r="179">
@@ -2401,7 +2401,7 @@
         <v>3.249999000000001</v>
       </c>
       <c r="C179" t="n">
-        <v>-9.824998999999996</v>
+        <v>-1.045835599999998</v>
       </c>
     </row>
     <row r="180">
@@ -2412,7 +2412,7 @@
         <v>3.274999000000001</v>
       </c>
       <c r="C180" t="n">
-        <v>-9.799998999999996</v>
+        <v>-1.020835599999998</v>
       </c>
     </row>
     <row r="181">
@@ -2423,7 +2423,7 @@
         <v>3.316666999999999</v>
       </c>
       <c r="C181" t="n">
-        <v>-9.758330999999998</v>
+        <v>-0.9791676000000002</v>
       </c>
     </row>
     <row r="182">
@@ -2434,7 +2434,7 @@
         <v>3.325001</v>
       </c>
       <c r="C182" t="n">
-        <v>-9.749996999999997</v>
+        <v>-0.9708335999999989</v>
       </c>
     </row>
   </sheetData>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>fixed_region</t>
+          <t>preceding_local_minimum</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="G2" t="n">
-        <v>13.074998</v>
+        <v>4.295834599999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="I2" t="n">
-        <v>13.074998</v>
+        <v>6.420831</v>
       </c>
       <c r="J2" t="n">
-        <v>9.829164999999996</v>
+        <v>2.124996400000001</v>
       </c>
     </row>
   </sheetData>
